--- a/results/CB/CorrectionsSplit.xlsx
+++ b/results/CB/CorrectionsSplit.xlsx
@@ -16358,7 +16358,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -16396,7 +16396,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16430,7 +16434,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -16455,7 +16459,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -16511,7 +16515,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -16583,7 +16587,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -16659,7 +16663,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -16731,7 +16735,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -16802,14 +16806,14 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J216" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -16827,7 +16831,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16840,7 +16844,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16874,14 +16882,14 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J217" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -16899,7 +16907,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -17259,7 +17267,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -17331,7 +17339,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -17706,14 +17714,14 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -17731,7 +17739,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17744,7 +17752,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17778,14 +17790,14 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J229" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -17803,7 +17815,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -18006,14 +18018,14 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J232" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -18031,7 +18043,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -18044,7 +18056,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -18078,14 +18094,14 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
       <c r="J233" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
@@ -18103,7 +18119,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -19213,14 +19229,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G248" t="n">
+        <v>30</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -19245,7 +19259,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -19258,7 +19272,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -19287,14 +19305,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G249" t="n">
+        <v>30</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -19319,7 +19335,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -19332,7 +19348,11 @@
           <t>ResponseTime</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -23162,7 +23182,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -23187,7 +23207,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -23200,7 +23220,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P300" t="inlineStr"/>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -23234,7 +23258,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -23259,7 +23283,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
